--- a/servers/maze_main_server_dev/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B92E63-605C-4F06-BAEB-F7F10A675302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8806A3C-ACB6-4CBE-8473-0C53B4522F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -206,10 +206,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9101,9201,9301,9401,9402,9403,9404,9501,9601,9701,3010000,3010101,3010201,3010301,3010401,3010402,3010403,3010404,3010405,3010501,3010601,3010701,3020000,3020101,3020201,3020301,3020401,3020502,3020603,3020704,3020805,3020501,3020601,3020701,3030000,3030101,3030201,3030301,3030401,3030502,3030603,3030704,3030805,3030501,3030601,3030701,3000101,3000201,3000301,3000401,3000501,3040101,3040102,3040201,3040202,3040301,3040401,3040501,3040601,3040701,3040801,3040901,3041001,3041101,3041102,3041201,3041301,3041401,3041501,3041601,3041701,3041801,3041901,3050000,3050001,3050101,3050102,3050301,3050401,3050501,3050601,3050701,3050801,3050901,3051001,3060000,3060001,3060101,3060102,3060301,3060401,3060501,3060601,3060701,3060801,3060901,3061001,3070000,3070001,3070101,3070102,3070301,3070401,3070501,3070601,3070701,3070801,3070901,3071001,3080000,3080001,3080101,3080102,3080301,3080401,3080501,3080601,3080701,3080801,3080901,3081001,3042001,3042002,3042101,3042102,3042201,3042202,3550100,3550200,3550205,3550206,3550300,3550400,3550500,3550501,3550502,3550503,3550600,3550700,3550701,3550702,3550703,3550800,3550900,3550901,3550902,3551000,3551100,3551101,3551102,3551103,3551200,3551300,3551301,3551302,3551303,3551304,3540100,3540200,3540201,3540205,3540207,3540300,3540400,3540401,3540402,3540405,3540407,3540500,3540600,3540601,3540602,3540605,3540607,3540700,3540800,3540801,3540802,3540805,3540807,3540900,3541000,3541001,3541002,3541005,3541007,3541100,3541200,3541201,3541205,3541207,3541300,3541400,3541401,3541405,3541407,3541500,3541600,3541601,3541602,3541605,3541607,3541700,3541800,3541801,3541802,3541805,3541807,3541900,3542000,3542001,3542002,3542005,3542007,3542100,3542200,3542201,3542202,3542205,3542207,3542300,3542400,3542401,3542405,3542407,3590100,3590200,3590201,3590206,3590300,3590400,3590401,3590402,3590403,3590405,3590407,3590500,3590600,3590601,3590602,3590700,3590800,3590801,3590802,3590805,3590900,3591000,3591001,3591005,3591100,3591200,3591300,3591400,3591401,3591402,3591500,3591600,3591601,3591700,3591800,3591801</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:1_3:2_5:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +219,10 @@
   </si>
   <si>
     <t>42711001:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3010101,3020101,3030101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -660,7 +660,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -848,7 +848,7 @@
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -873,13 +873,13 @@
         <v>801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8806A3C-ACB6-4CBE-8473-0C53B4522F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FF830-EEFE-4B1A-9EFE-05157DB7791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -210,10 +210,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>地宫普攻动作档位和普攻目标个数关系（key-个数，value-档次）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>张炽阳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +219,18 @@
   </si>
   <si>
     <t>3010101,3020101,3030101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地宫普攻动作档位和普攻目标个数关系（key-个数，value-档次）（废弃）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地宫普攻动作档位增加普攻目标个数关系（key-档次，value-个数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:0_2:1_3:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -567,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -660,7 +668,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -848,7 +856,7 @@
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -873,13 +881,27 @@
         <v>801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>802</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
